--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VS Code Projects\ArrangeTeacher\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9787BA-ABC9-4675-B4B7-E982D0F68BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CA4CA1-12A7-4D9F-B0A5-6D45C6E856C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="1740" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -600,7 +600,7 @@
         <v>11</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
